--- a/one up/普物實驗/Lab11 彈簧縱波的駐波實驗/E24146107_王翊權_預報11_表格.xlsx
+++ b/one up/普物實驗/Lab11 彈簧縱波的駐波實驗/E24146107_王翊權_預報11_表格.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one up\普物實驗\Lab11 彈簧縱波的駐波實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB7FE972-F71C-497C-AD8A-FAA51AC13188}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F320BB-D1CC-4608-99E4-150E3C144FC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="18648" windowHeight="11784" activeTab="1" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="15">
   <si>
     <t>#1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,6 +85,14 @@
   </si>
   <si>
     <t>k</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原長</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -488,12 +496,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3419739-BEEB-4B53-8EC5-6DC56A0166CA}">
   <dimension ref="A4:G16"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.7265625" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -501,10 +509,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" s="1">
+        <v>11.3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1"/>
       <c r="C6" s="1" t="s">
         <v>0</v>
@@ -522,27 +532,35 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="C7" s="1">
+        <v>24.5</v>
+      </c>
+      <c r="D7" s="1">
+        <v>28</v>
+      </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
+      <c r="C8" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="D8" s="1">
+        <v>12.5</v>
+      </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
@@ -552,7 +570,7 @@
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -560,10 +578,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="B12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" s="1"/>
       <c r="C13" s="1" t="s">
         <v>0</v>
@@ -581,27 +601,23 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
+        <v>13</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B16" s="1" t="s">
         <v>6</v>
       </c>
@@ -614,33 +630,47 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0221AA1A-1987-4F82-96E4-FD9B3B087DF3}">
-  <dimension ref="A2:I8"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
+  <dimension ref="A2:J11"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
+      <c r="C3" s="1">
+        <v>150</v>
+      </c>
+      <c r="D3" s="1">
+        <v>200</v>
+      </c>
+      <c r="E3" s="1">
+        <v>250</v>
+      </c>
+      <c r="F3" s="1">
+        <v>300</v>
+      </c>
+      <c r="G3" s="1">
+        <v>350</v>
+      </c>
       <c r="I3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
@@ -649,36 +679,52 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
-      <c r="I4" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="I4" s="1">
+        <v>10</v>
+      </c>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B7" s="1" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="I7" s="1" t="s">
+      <c r="C10" s="1">
+        <v>10</v>
+      </c>
+      <c r="D10" s="1">
+        <v>20</v>
+      </c>
+      <c r="E10" s="1">
+        <v>30</v>
+      </c>
+      <c r="F10" s="1">
+        <v>40</v>
+      </c>
+      <c r="G10" s="1">
+        <v>50</v>
+      </c>
+      <c r="I10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
-      <c r="B8" s="1" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="I8" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="J11" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
